--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFHauptdiagnosegruppen-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFHauptdiagnosegruppen-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T09:28:26+00:00</t>
+    <t>2025-02-06T11:21:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFHauptdiagnosegruppen-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFHauptdiagnosegruppen-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-06T11:21:55+00:00</t>
+    <t>2025-02-06T12:00:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFHauptdiagnosegruppen-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFHauptdiagnosegruppen-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-06T12:00:33+00:00</t>
+    <t>2025-02-10T09:34:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFHauptdiagnosegruppen-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFHauptdiagnosegruppen-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T09:34:03+00:00</t>
+    <t>2025-02-10T11:21:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFHauptdiagnosegruppen-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFHauptdiagnosegruppen-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T11:21:18+00:00</t>
+    <t>2025-02-10T11:27:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFHauptdiagnosegruppen-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFHauptdiagnosegruppen-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T11:27:45+00:00</t>
+    <t>2025-02-12T10:32:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFHauptdiagnosegruppen-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFHauptdiagnosegruppen-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-12T10:32:14+00:00</t>
+    <t>2025-02-12T10:54:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFHauptdiagnosegruppen-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFHauptdiagnosegruppen-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-12T10:54:19+00:00</t>
+    <t>2025-02-13T11:55:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFHauptdiagnosegruppen-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFHauptdiagnosegruppen-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T11:55:14+00:00</t>
+    <t>2025-02-13T12:01:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFHauptdiagnosegruppen-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFHauptdiagnosegruppen-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T12:01:49+00:00</t>
+    <t>2025-02-13T12:22:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFHauptdiagnosegruppen-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFHauptdiagnosegruppen-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T12:22:49+00:00</t>
+    <t>2025-02-13T12:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFHauptdiagnosegruppen-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFHauptdiagnosegruppen-valueset.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://example.org/ValueSet/moped-LKFHauptdiagnosegruppen-valueset</t>
+    <t>https://elga.moped.at/ValueSet/moped-LKFHauptdiagnosegruppen-valueset</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,19 +57,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T12:31:02+00:00</t>
+    <t>2025-02-13T14:17:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>Example Publisher</t>
+    <t>ELGA GmbH</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>Example Publisher (http://example.org/example-publisher)</t>
+    <t>ELGA GmbH (https://elga.gv.at)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFHauptdiagnosegruppen-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFHauptdiagnosegruppen-valueset.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="469">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:17:28+00:00</t>
+    <t>2025-02-13T14:29:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,13 +96,1324 @@
     <t>Concept</t>
   </si>
   <si>
+    <t>HDG01.01</t>
+  </si>
+  <si>
+    <t>Infektiöse Erkrankung des Gehirns/Rückenmarks und seiner Häute</t>
+  </si>
+  <si>
+    <t>HDG01.02</t>
+  </si>
+  <si>
+    <t>Maligne Neoplasien – Nervensystem</t>
+  </si>
+  <si>
+    <t>HDG01.03</t>
+  </si>
+  <si>
+    <t>Benigne Neoplasien und Abszesse – Nervensystem</t>
+  </si>
+  <si>
+    <t>HDG01.04</t>
+  </si>
+  <si>
+    <t>Zerebrale Degeneration/Kindheit</t>
+  </si>
+  <si>
+    <t>HDG01.05</t>
+  </si>
+  <si>
+    <t>Systematrophien und andere Degenerationen des Nervensystems</t>
+  </si>
+  <si>
+    <t>HDG01.06</t>
+  </si>
+  <si>
+    <t>Parkinson-Syndrom</t>
+  </si>
+  <si>
+    <t>HDG01.07</t>
+  </si>
+  <si>
+    <t>Andere extrapyramidale Erkrankungen</t>
+  </si>
+  <si>
+    <t>HDG01.08</t>
+  </si>
+  <si>
+    <t>Essentieller Tremor/Tick</t>
+  </si>
+  <si>
+    <t>HDG01.09</t>
+  </si>
+  <si>
+    <t>Hereditäre und idiopathische Erkrankungen</t>
+  </si>
+  <si>
+    <t>HDG01.10</t>
+  </si>
+  <si>
+    <t>Multiple Sklerose und andere demyelinisierende Erkrankungen des zentralen Nervensystems</t>
+  </si>
+  <si>
+    <t>HDG01.11</t>
+  </si>
+  <si>
+    <t>Zerebrale Kinderlähmung</t>
+  </si>
+  <si>
+    <t>HDG01.12</t>
+  </si>
+  <si>
+    <t>Epilepsie</t>
+  </si>
+  <si>
+    <t>HDG01.13</t>
+  </si>
+  <si>
+    <t>Primäre Kopfschmerzen</t>
+  </si>
+  <si>
+    <t>HDG01.14</t>
+  </si>
+  <si>
+    <t>Erkrankungen der Hirnnerven</t>
+  </si>
+  <si>
+    <t>HDG01.15</t>
+  </si>
+  <si>
+    <t>Erkrankungen der Spinalnerven/Nervenwurzeln</t>
+  </si>
+  <si>
+    <t>HDG01.16</t>
+  </si>
+  <si>
+    <t>Mononeuropathien</t>
+  </si>
+  <si>
+    <t>HDG01.17</t>
+  </si>
+  <si>
+    <t>Erkrankungen der Nervengeflechte</t>
+  </si>
+  <si>
+    <t>HDG01.18</t>
+  </si>
+  <si>
+    <t>Polyneuropathien</t>
+  </si>
+  <si>
+    <t>HDG01.19</t>
+  </si>
+  <si>
+    <t>Myasthenie und akute Polyradikuloneuritis</t>
+  </si>
+  <si>
+    <t>HDG01.20</t>
+  </si>
+  <si>
+    <t>Subarachnoidalblutung</t>
+  </si>
+  <si>
+    <t>HDG01.21</t>
+  </si>
+  <si>
+    <t>Intrazerebrale Blutungen</t>
+  </si>
+  <si>
+    <t>HDG01.22</t>
+  </si>
+  <si>
+    <t>Ischämische zerebrale Erkrankungen</t>
+  </si>
+  <si>
+    <t>HDG01.23</t>
+  </si>
+  <si>
+    <t>Transiente ischämische Attacken</t>
+  </si>
+  <si>
+    <t>HDG01.24</t>
+  </si>
+  <si>
+    <t>Andere Hirngefäßerkrankungen und Spätfolgen</t>
+  </si>
+  <si>
+    <t>HDG01.25</t>
+  </si>
+  <si>
+    <t>Kongenitale Anomalien - Nervensystem</t>
+  </si>
+  <si>
+    <t>HDG01.26</t>
+  </si>
+  <si>
+    <t>Schädelfrakturen</t>
+  </si>
+  <si>
+    <t>HDG01.27</t>
+  </si>
+  <si>
+    <t>Frakturen und Luxationen der Wirbelsäule mit/ohne Rückenmarksverletzungen</t>
+  </si>
+  <si>
+    <t>HDG01.28</t>
+  </si>
+  <si>
+    <t>Commotio cerebri</t>
+  </si>
+  <si>
+    <t>HDG01.29</t>
+  </si>
+  <si>
+    <t>Contusio cerebri</t>
+  </si>
+  <si>
+    <t>HDG01.30</t>
+  </si>
+  <si>
+    <t>Spätfolgen von Verletzungen des Nervensystems</t>
+  </si>
+  <si>
+    <t>HDG01.31</t>
+  </si>
+  <si>
+    <t>Sonstige Erkrankungen - Nervensystem</t>
+  </si>
+  <si>
+    <t>HDG01.32</t>
+  </si>
+  <si>
+    <t>Lokale und pseudoradikuläre Syndrome der Wirbelsäule</t>
+  </si>
+  <si>
+    <t>HDG01.33</t>
+  </si>
+  <si>
+    <t>Myelopathien unterschiedlicher Genese</t>
+  </si>
+  <si>
+    <t>HDG01.34</t>
+  </si>
+  <si>
+    <t>Chronische Schmerzsyndrome</t>
+  </si>
+  <si>
+    <t>HDG02.01</t>
+  </si>
+  <si>
+    <t>Infektionen im Nasen-/Rachenbereich</t>
+  </si>
+  <si>
+    <t>HDG02.02</t>
+  </si>
+  <si>
+    <t>Maligne Neoplasien - HNO</t>
+  </si>
+  <si>
+    <t>HDG02.03</t>
+  </si>
+  <si>
+    <t>Benigne Neoplasien - HNO</t>
+  </si>
+  <si>
+    <t>HDG02.04</t>
+  </si>
+  <si>
+    <t>Erkrankungen des Ohres/Mittelohres</t>
+  </si>
+  <si>
+    <t>HDG02.06</t>
+  </si>
+  <si>
+    <t>Komplizierte Mittelohraffektionen</t>
+  </si>
+  <si>
+    <t>HDG02.07</t>
+  </si>
+  <si>
+    <t>Otoneuropathien</t>
+  </si>
+  <si>
+    <t>HDG02.08</t>
+  </si>
+  <si>
+    <t>Sonstige Erkrankungen Nase, Nasennebenhöhlen, Rachen</t>
+  </si>
+  <si>
+    <t>HDG02.09</t>
+  </si>
+  <si>
+    <t>Akute Affektionen Nase, NNH, Rachen, obere Luftwege</t>
+  </si>
+  <si>
+    <t>HDG02.10</t>
+  </si>
+  <si>
+    <t>Chronische Affektionen der Nase</t>
+  </si>
+  <si>
+    <t>HDG02.11</t>
+  </si>
+  <si>
+    <t>Chronische Rachenaffektionen</t>
+  </si>
+  <si>
+    <t>HDG02.12</t>
+  </si>
+  <si>
+    <t>Chronische Affektionen des Larynx</t>
+  </si>
+  <si>
+    <t>HDG02.13</t>
+  </si>
+  <si>
+    <t>Kongenitale Anomalien im HNO-Bereich</t>
+  </si>
+  <si>
+    <t>HDG02.14</t>
+  </si>
+  <si>
+    <t>Traumen im HNO-Bereich</t>
+  </si>
+  <si>
+    <t>HDG03.01</t>
+  </si>
+  <si>
+    <t>Maligne Neoplasien des Auges</t>
+  </si>
+  <si>
+    <t>HDG03.02</t>
+  </si>
+  <si>
+    <t>Operative Diagnosen am Auge</t>
+  </si>
+  <si>
+    <t>HDG03.03</t>
+  </si>
+  <si>
+    <t>Augen-Diagnosen I</t>
+  </si>
+  <si>
+    <t>HDG03.04</t>
+  </si>
+  <si>
+    <t>Augen-Diagnosen II</t>
+  </si>
+  <si>
+    <t>HDG03.05</t>
+  </si>
+  <si>
+    <t>Augen-Diagnosen III</t>
+  </si>
+  <si>
+    <t>HDG03.06</t>
+  </si>
+  <si>
+    <t>Augen-Diagnosen IV</t>
+  </si>
+  <si>
+    <t>HDG03.07</t>
+  </si>
+  <si>
+    <t>Augen-Diagnosen V</t>
+  </si>
+  <si>
+    <t>HDG03.08</t>
+  </si>
+  <si>
+    <t>Augen-Diagnosen VI</t>
+  </si>
+  <si>
+    <t>HDG04.01</t>
+  </si>
+  <si>
+    <t>Akute Affektionen der Mundhöhle</t>
+  </si>
+  <si>
+    <t>HDG04.02</t>
+  </si>
+  <si>
+    <t>Sonstige Erkrankungen Zähne/Zahnhalteapparat/Mundhöhle</t>
+  </si>
+  <si>
+    <t>HDG04.03</t>
+  </si>
+  <si>
+    <t>Krankheiten der Kiefer</t>
+  </si>
+  <si>
+    <t>HDG04.04</t>
+  </si>
+  <si>
+    <t>Dentofaziale Anomalien</t>
+  </si>
+  <si>
+    <t>HDG04.05</t>
+  </si>
+  <si>
+    <t>Frakturen der Gesichtsknochen</t>
+  </si>
+  <si>
+    <t>HDG05.01</t>
+  </si>
+  <si>
+    <t>Tuberkulose</t>
+  </si>
+  <si>
+    <t>HDG05.02</t>
+  </si>
+  <si>
+    <t>Akute Affektionen der mittleren Atemwege und Atelektase</t>
+  </si>
+  <si>
+    <t>HDG05.03</t>
+  </si>
+  <si>
+    <t>Pneumonie und Bronchiolitis</t>
+  </si>
+  <si>
+    <t>HDG05.04</t>
+  </si>
+  <si>
+    <t>Chronische Bronchialerkrankungen und Emphysem</t>
+  </si>
+  <si>
+    <t>HDG05.05</t>
+  </si>
+  <si>
+    <t>Maligne Neoplasien der unteren Atmungsorgane</t>
+  </si>
+  <si>
+    <t>HDG05.06</t>
+  </si>
+  <si>
+    <t>Benigne Neoplasien der unteren Atmungsorgane</t>
+  </si>
+  <si>
+    <t>HDG05.07</t>
+  </si>
+  <si>
+    <t>Diffuse Lungenparenchymerkrankungen</t>
+  </si>
+  <si>
+    <t>HDG05.08</t>
+  </si>
+  <si>
+    <t>Erkrankungen des Pleuraraumes</t>
+  </si>
+  <si>
+    <t>HDG05.09</t>
+  </si>
+  <si>
+    <t>Kongenitale Anomalien der Atmungsorgane</t>
+  </si>
+  <si>
+    <t>HDG05.10</t>
+  </si>
+  <si>
+    <t>Larynx- Thoraxverletzungen außer Herz</t>
+  </si>
+  <si>
+    <t>HDG05.11</t>
+  </si>
+  <si>
+    <t>Affektionen der Atmungsorgane</t>
+  </si>
+  <si>
+    <t>HDG06.02</t>
+  </si>
+  <si>
+    <t>Hypertonie</t>
+  </si>
+  <si>
+    <t>HDG06.03</t>
+  </si>
+  <si>
+    <t>Linksherzinsuffizienz und akute Herzerkrankungen</t>
+  </si>
+  <si>
+    <t>HDG06.04</t>
+  </si>
+  <si>
+    <t>Chronische Herzerkrankungen</t>
+  </si>
+  <si>
+    <t>HDG06.05</t>
+  </si>
+  <si>
+    <t>Akute entzündliche Herzkrankheiten</t>
+  </si>
+  <si>
+    <t>HDG06.06</t>
+  </si>
+  <si>
+    <t>Herzklappenfehler und Kardiomyopathie</t>
+  </si>
+  <si>
+    <t>HDG06.07</t>
+  </si>
+  <si>
+    <t>Komplizierte Herzrhythmusstörungen</t>
+  </si>
+  <si>
+    <t>HDG06.08</t>
+  </si>
+  <si>
+    <t>Herzrhythmusstörungen</t>
+  </si>
+  <si>
+    <t>HDG06.09</t>
+  </si>
+  <si>
+    <t>Aortenaneurysmen, andere Affektionen der Aorta</t>
+  </si>
+  <si>
+    <t>HDG06.10</t>
+  </si>
+  <si>
+    <t>Symptome und Zustände betreffend Herz und Kreislauf</t>
+  </si>
+  <si>
+    <t>HDG06.11</t>
+  </si>
+  <si>
+    <t>Kongenitale Anomalien des Herzens und der großen Gefäße</t>
+  </si>
+  <si>
+    <t>HDG07.01</t>
+  </si>
+  <si>
+    <t>Nichtentzündliche Affektionen der Arterien, außer Aorta</t>
+  </si>
+  <si>
+    <t>HDG07.02</t>
+  </si>
+  <si>
+    <t>Entzündliche Affektionen der Arterien</t>
+  </si>
+  <si>
+    <t>HDG07.04</t>
+  </si>
+  <si>
+    <t>Affektionen der Venen</t>
+  </si>
+  <si>
+    <t>HDG07.05</t>
+  </si>
+  <si>
+    <t>Komplizierte Affektionen der Venen</t>
+  </si>
+  <si>
+    <t>HDG07.06</t>
+  </si>
+  <si>
+    <t>Verletzung der peripheren Blutgefäße</t>
+  </si>
+  <si>
+    <t>HDG07.07</t>
+  </si>
+  <si>
+    <t>Affektionen des Lymphsystems</t>
+  </si>
+  <si>
+    <t>HDG08.01</t>
+  </si>
+  <si>
+    <t>Maligne Neoplasien des Gastrointestinums</t>
+  </si>
+  <si>
+    <t>HDG08.02</t>
+  </si>
+  <si>
+    <t>Maligne Neoplasien Leber, Galle, Pankreas</t>
+  </si>
+  <si>
+    <t>HDG08.03</t>
+  </si>
+  <si>
+    <t>Benigne Neoplasien des Gastrointestinaltrakts</t>
+  </si>
+  <si>
+    <t>HDG08.04</t>
+  </si>
+  <si>
+    <t>Einfache Affektionen Ösophagus, Magen, Duodenum</t>
+  </si>
+  <si>
+    <t>HDG08.05</t>
+  </si>
+  <si>
+    <t>Komplizierte Affektionen Ösophagus, Magen, Duodenum</t>
+  </si>
+  <si>
+    <t>HDG08.06</t>
+  </si>
+  <si>
+    <t>Appendicitis und Darmdivertikel</t>
+  </si>
+  <si>
+    <t>HDG08.07</t>
+  </si>
+  <si>
+    <t>Komplizierte abdominale Hernien</t>
+  </si>
+  <si>
+    <t>HDG08.08</t>
+  </si>
+  <si>
+    <t>Chronisch entzündliche Darmerkrankung</t>
+  </si>
+  <si>
+    <t>HDG08.09</t>
+  </si>
+  <si>
+    <t>Malabsorption</t>
+  </si>
+  <si>
+    <t>HDG08.10</t>
+  </si>
+  <si>
+    <t>Komplizierte Darmerkrankungen</t>
+  </si>
+  <si>
+    <t>HDG08.11</t>
+  </si>
+  <si>
+    <t>Sonstige Magen-Darm Affektionen</t>
+  </si>
+  <si>
+    <t>HDG08.12</t>
+  </si>
+  <si>
+    <t>Komplizierte anorektale Erkrankungen</t>
+  </si>
+  <si>
+    <t>HDG08.13</t>
+  </si>
+  <si>
+    <t>Andere anorektale Erkrankungen</t>
+  </si>
+  <si>
+    <t>HDG08.14</t>
+  </si>
+  <si>
+    <t>Akute Hepatitis</t>
+  </si>
+  <si>
+    <t>HDG08.15</t>
+  </si>
+  <si>
+    <t>Erkrankungen von Leber, Galle, Pankreas</t>
+  </si>
+  <si>
+    <t>HDG08.16</t>
+  </si>
+  <si>
+    <t>Komplizierte Erkrankungen von Leber, Galle, Pankreas</t>
+  </si>
+  <si>
+    <t>HDG08.17</t>
+  </si>
+  <si>
+    <t>Kongenitale Anomalien des Verdauungstraktes</t>
+  </si>
+  <si>
+    <t>HDG08.18</t>
+  </si>
+  <si>
+    <t>Symptome und Zustände betreffend Verdauungssystem</t>
+  </si>
+  <si>
+    <t>HDG08.19</t>
+  </si>
+  <si>
+    <t>Verletzung intraabdominaler Organe und Blutgefäße</t>
+  </si>
+  <si>
+    <t>HDG09.01</t>
+  </si>
+  <si>
+    <t>Andere Infektionen der Urogenitalorgane</t>
+  </si>
+  <si>
+    <t>HDG09.02</t>
+  </si>
+  <si>
+    <t>Maligne Neoplasien der Harnblase, Niere, anderer Harnorgane</t>
+  </si>
+  <si>
+    <t>HDG09.03</t>
+  </si>
+  <si>
+    <t>Benigne Neoplasien der Niere und anderer Harnorgane</t>
+  </si>
+  <si>
+    <t>HDG09.04</t>
+  </si>
+  <si>
+    <t>Nephropathie</t>
+  </si>
+  <si>
+    <t>HDG09.05</t>
+  </si>
+  <si>
+    <t>Urethralsyndrom</t>
+  </si>
+  <si>
+    <t>HDG09.06</t>
+  </si>
+  <si>
+    <t>Nephropathie mit schweren systemischen Komplikationen</t>
+  </si>
+  <si>
+    <t>HDG09.07</t>
+  </si>
+  <si>
+    <t>Nephrolithiasis</t>
+  </si>
+  <si>
+    <t>HDG09.08</t>
+  </si>
+  <si>
+    <t>Affektionen der ableitenden Harnwege</t>
+  </si>
+  <si>
+    <t>HDG09.09</t>
+  </si>
+  <si>
+    <t>Verletzungen der Beckenorgane und Niere</t>
+  </si>
+  <si>
+    <t>HDG10.01</t>
+  </si>
+  <si>
+    <t>Maligne Neoplasien der Prostata, Hoden, Penis, andere</t>
+  </si>
+  <si>
+    <t>HDG10.02</t>
+  </si>
+  <si>
+    <t>Benigne Neoplasien der Genitalorgane</t>
+  </si>
+  <si>
+    <t>HDG10.03</t>
+  </si>
+  <si>
+    <t>Erkrankungen der Prostata und der äußeren Genitale</t>
+  </si>
+  <si>
+    <t>HDG10.04</t>
+  </si>
+  <si>
+    <t>Affektionen der äußeren Genitale</t>
+  </si>
+  <si>
+    <t>HDG10.05</t>
+  </si>
+  <si>
+    <t>Verletzungen der Genitalorgane</t>
+  </si>
+  <si>
+    <t>HDG11.01</t>
+  </si>
+  <si>
+    <t>Maligne Neoplasien der weiblichen Genitalorgane</t>
+  </si>
+  <si>
+    <t>HDG11.02</t>
+  </si>
+  <si>
+    <t>Benigne Neoplasien der weiblichen Genitalorgane</t>
+  </si>
+  <si>
+    <t>HDG11.03</t>
+  </si>
+  <si>
+    <t>Akute entzündliche Erkrankungen der weiblichen Genitalorgane</t>
+  </si>
+  <si>
+    <t>HDG11.04</t>
+  </si>
+  <si>
+    <t>Chronische entzündliche Erkrankungen der weiblichen Genitalorgane</t>
+  </si>
+  <si>
+    <t>HDG11.05</t>
+  </si>
+  <si>
+    <t>Lageanomalien des Uterus</t>
+  </si>
+  <si>
+    <t>HDG11.06</t>
+  </si>
+  <si>
+    <t>Nichtentzündliche Affektionen der Adnexe</t>
+  </si>
+  <si>
+    <t>HDG11.07</t>
+  </si>
+  <si>
+    <t>Funktionelle Störungen der weiblichen Genitalorgane</t>
+  </si>
+  <si>
+    <t>HDG11.08</t>
+  </si>
+  <si>
+    <t>Nichtentzündliche Affektionen des Uterus, Vagina, Vulva inklusive Dysplasien</t>
+  </si>
+  <si>
+    <t>HDG11.09</t>
+  </si>
+  <si>
+    <t>Sonstige Erkrankungen der weiblichen Genitalorgane</t>
+  </si>
+  <si>
+    <t>HDG11.10</t>
+  </si>
+  <si>
+    <t>Kongenitale Anomalien der weiblichen Genitalorgane</t>
+  </si>
+  <si>
+    <t>HDG12.01</t>
+  </si>
+  <si>
+    <t>Abortus</t>
+  </si>
+  <si>
+    <t>HDG12.03</t>
+  </si>
+  <si>
+    <t>Blutung in der Spätschwangerschaft</t>
+  </si>
+  <si>
+    <t>HDG12.04</t>
+  </si>
+  <si>
+    <t>Komplikationen in der Schwangerschaft und im Wochenbett</t>
+  </si>
+  <si>
+    <t>HDG12.07</t>
+  </si>
+  <si>
+    <t>Peri-/postpartale Komplikationen</t>
+  </si>
+  <si>
+    <t>HDG13.01</t>
+  </si>
+  <si>
+    <t>Schwere fetale Schädigungen</t>
+  </si>
+  <si>
+    <t>HDG13.02</t>
+  </si>
+  <si>
+    <t>Leichte fetale Schädigungen</t>
+  </si>
+  <si>
+    <t>HDG14.01</t>
+  </si>
+  <si>
+    <t>Maligne Neoplasien von Knochen, Bindegewebe und Weichteilen</t>
+  </si>
+  <si>
+    <t>HDG14.02</t>
+  </si>
+  <si>
+    <t>Benigne Neoplasien von Knochen, Bindegewebe und Weichteilen</t>
+  </si>
+  <si>
+    <t>HDG14.03</t>
+  </si>
+  <si>
+    <t>Osteomyelitis und akute Arthritis</t>
+  </si>
+  <si>
+    <t>HDG14.04</t>
+  </si>
+  <si>
+    <t>Chronisch entzündliche und degenerative Erkrankungen am Bewegungsapparat</t>
+  </si>
+  <si>
+    <t>HDG14.05</t>
+  </si>
+  <si>
+    <t>Affektionen der Weichteile am Bewegungsapparat</t>
+  </si>
+  <si>
+    <t>HDG14.06</t>
+  </si>
+  <si>
+    <t>Anomalien und Deformitäten des Bewegungsapparates</t>
+  </si>
+  <si>
+    <t>HDG14.07</t>
+  </si>
+  <si>
+    <t>Andere Affektionen am Bewegungsapparat</t>
+  </si>
+  <si>
+    <t>HDG14.08</t>
+  </si>
+  <si>
+    <t>Spätfolgen von Verletzungen von Muskeln, Skelett, Bindegewebe, Haut</t>
+  </si>
+  <si>
+    <t>HDG15.01</t>
+  </si>
+  <si>
+    <t>Frakturen der oberen Extremität, außer Hand</t>
+  </si>
+  <si>
+    <t>HDG15.02</t>
+  </si>
+  <si>
+    <t>Frakturen Hand/Vorfuß</t>
+  </si>
+  <si>
+    <t>HDG15.03</t>
+  </si>
+  <si>
+    <t>Frakturen der unteren Extremität/Becken, außer Vorfuß</t>
+  </si>
+  <si>
+    <t>HDG15.04</t>
+  </si>
+  <si>
+    <t>Luxationen, Distorsionen, Kontusionen, Quetschungen</t>
+  </si>
+  <si>
+    <t>HDG15.05</t>
+  </si>
+  <si>
+    <t>Kniegelenkschädigungen</t>
+  </si>
+  <si>
+    <t>HDG15.06</t>
+  </si>
+  <si>
+    <t>Hautverletzungen, Verbrennungen Grad I-II</t>
+  </si>
+  <si>
+    <t>HDG15.07</t>
+  </si>
+  <si>
+    <t>Verbrennungen großflächig, Grad III-IV</t>
+  </si>
+  <si>
+    <t>HDG15.08</t>
+  </si>
+  <si>
+    <t>Traumatische Amputationen</t>
+  </si>
+  <si>
+    <t>HDG16.01</t>
+  </si>
+  <si>
+    <t>Komplizierte Infektionen des Verdauungstraktes</t>
+  </si>
+  <si>
+    <t>HDG16.02</t>
+  </si>
+  <si>
+    <t>Andere Infektionen des Verdauungstraktes</t>
+  </si>
+  <si>
+    <t>HDG16.03</t>
+  </si>
+  <si>
+    <t>Bakterielle Zoonosen</t>
+  </si>
+  <si>
+    <t>HDG16.04</t>
+  </si>
+  <si>
+    <t>Andere bakterielle Krankheiten</t>
+  </si>
+  <si>
+    <t>HDG16.05</t>
+  </si>
+  <si>
+    <t>Komplizierte bakterielle Infektionen, Sepsis</t>
+  </si>
+  <si>
+    <t>HDG16.06</t>
+  </si>
+  <si>
+    <t>Virusinfektionen</t>
+  </si>
+  <si>
+    <t>HDG16.07</t>
+  </si>
+  <si>
+    <t>Nichtheimische Infektionen durch Protozoen</t>
+  </si>
+  <si>
+    <t>HDG16.08</t>
+  </si>
+  <si>
+    <t>Mykosen</t>
+  </si>
+  <si>
+    <t>HDG16.09</t>
+  </si>
+  <si>
+    <t>Andere infektiöse und parasitäre Krankheiten</t>
+  </si>
+  <si>
+    <t>HDG16.10</t>
+  </si>
+  <si>
+    <t>Helminthosen</t>
+  </si>
+  <si>
+    <t>HDG16.11</t>
+  </si>
+  <si>
+    <t>Befunde und Zustände betreffend Infektionen</t>
+  </si>
+  <si>
+    <t>HDG16.12</t>
+  </si>
+  <si>
+    <t>AIDS-Erkrankung</t>
+  </si>
+  <si>
+    <t>HDG16.13</t>
+  </si>
+  <si>
+    <t>HIV-Infektion und assoziierte Erkrankungen</t>
+  </si>
+  <si>
+    <t>HDG17.01</t>
+  </si>
+  <si>
+    <t>Akute Leukämie</t>
+  </si>
+  <si>
+    <t>HDG17.02</t>
+  </si>
+  <si>
+    <t>Hochmaligne Non-Hodgkin Lymphome</t>
+  </si>
+  <si>
+    <t>HDG17.03</t>
+  </si>
+  <si>
+    <t>Morbus Hodgkin</t>
+  </si>
+  <si>
+    <t>HDG17.04</t>
+  </si>
+  <si>
+    <t>Andere hämatologische Neoplasien</t>
+  </si>
+  <si>
+    <t>HDG17.05</t>
+  </si>
+  <si>
+    <t>Mangelanämien</t>
+  </si>
+  <si>
+    <t>HDG17.06</t>
+  </si>
+  <si>
+    <t>Andere Erkrankungen des Blutes</t>
+  </si>
+  <si>
+    <t>HDG17.07</t>
+  </si>
+  <si>
+    <t>Aplastische Anämien</t>
+  </si>
+  <si>
+    <t>HDG17.08</t>
+  </si>
+  <si>
+    <t>Koagulopathien</t>
+  </si>
+  <si>
+    <t>HDG18.01</t>
+  </si>
+  <si>
+    <t>Maligne Neoplasien anderer endokriner Drüsen</t>
+  </si>
+  <si>
+    <t>HDG18.02</t>
+  </si>
+  <si>
+    <t>Benigne Neoplasien anderer endokriner Drüsen</t>
+  </si>
+  <si>
+    <t>HDG18.03</t>
+  </si>
+  <si>
+    <t>Erkrankungen der Schilddrüse und Nebenschilddrüse</t>
+  </si>
+  <si>
+    <t>HDG18.04</t>
+  </si>
+  <si>
+    <t>Diabetisches Koma u. komplizierte Stoffwechselstörungen</t>
+  </si>
+  <si>
+    <t>HDG18.05</t>
+  </si>
+  <si>
+    <t>Erkrankungen der Bauchspeicheldrüse</t>
+  </si>
+  <si>
+    <t>HDG18.06</t>
+  </si>
+  <si>
+    <t>Sekretionsstörungen der Hypophyse und Nebenniere</t>
+  </si>
+  <si>
+    <t>HDG18.07</t>
+  </si>
+  <si>
+    <t>Funktionsstörungen der Gonaden</t>
+  </si>
+  <si>
+    <t>HDG18.08</t>
+  </si>
+  <si>
+    <t>Andere endokrine Störungen</t>
+  </si>
+  <si>
+    <t>HDG18.09</t>
+  </si>
+  <si>
+    <t>Mangelerkrankungen und Störungen des Flüssigkeitshaushaltes</t>
+  </si>
+  <si>
+    <t>HDG18.10</t>
+  </si>
+  <si>
+    <t>Stoffwechselstörungen</t>
+  </si>
+  <si>
+    <t>HDG19.03</t>
+  </si>
+  <si>
+    <t>Andere Erkrankungen der Mamma</t>
+  </si>
+  <si>
+    <t>HDG19.04</t>
+  </si>
+  <si>
+    <t>Virale Infektionen der Haut</t>
+  </si>
+  <si>
+    <t>HDG19.05</t>
+  </si>
+  <si>
+    <t>Geschlechtskrankheiten</t>
+  </si>
+  <si>
+    <t>HDG19.06</t>
+  </si>
+  <si>
+    <t>Einfache Mykosen</t>
+  </si>
+  <si>
+    <t>HDG19.07</t>
+  </si>
+  <si>
+    <t>Komplizierte Affektionen der Haut</t>
+  </si>
+  <si>
+    <t>HDG19.08</t>
+  </si>
+  <si>
+    <t>Einfache Affektionen der Haut</t>
+  </si>
+  <si>
+    <t>HDG19.09</t>
+  </si>
+  <si>
+    <t>Kollagenosen und Sarkoidose</t>
+  </si>
+  <si>
+    <t>HDG19.10</t>
+  </si>
+  <si>
+    <t>Maligne Neoplasien der Haut</t>
+  </si>
+  <si>
+    <t>HDG19.11</t>
+  </si>
+  <si>
+    <t>Benigne Neoplasien der Haut</t>
+  </si>
+  <si>
+    <t>HDG19.12</t>
+  </si>
+  <si>
+    <t>Maligne Neoplasien der Mamma</t>
+  </si>
+  <si>
+    <t>HDG19.13</t>
+  </si>
+  <si>
+    <t>Benigne Neoplasien der Mamma</t>
+  </si>
+  <si>
+    <t>HDG20.01</t>
+  </si>
+  <si>
+    <t>Alzheimersche Krankheit und nicht-vaskuläre Demenzen</t>
+  </si>
+  <si>
+    <t>HDG20.02</t>
+  </si>
+  <si>
+    <t>Demenzen mit psychiatrischen Syndromen</t>
+  </si>
+  <si>
+    <t>HDG20.03</t>
+  </si>
+  <si>
+    <t>Vaskuläre Demenz</t>
+  </si>
+  <si>
+    <t>HDG20.04</t>
+  </si>
+  <si>
+    <t>Alkoholentzugssyndrom und -psychosen</t>
+  </si>
+  <si>
+    <t>HDG20.06</t>
+  </si>
+  <si>
+    <t>Drogenentzugssyndrome und -psychosen</t>
+  </si>
+  <si>
+    <t>HDG20.08</t>
+  </si>
+  <si>
+    <t>Akute exogene Reaktionstypen/ Psychogene Reaktion</t>
+  </si>
+  <si>
+    <t>HDG20.09</t>
+  </si>
+  <si>
+    <t>Schizophrene Psychosen</t>
+  </si>
+  <si>
+    <t>HDG20.10</t>
+  </si>
+  <si>
+    <t>Affektive Psychosen</t>
+  </si>
+  <si>
+    <t>HDG20.11</t>
+  </si>
+  <si>
+    <t>Psychosen des Kindesalters</t>
+  </si>
+  <si>
+    <t>HDG20.12</t>
+  </si>
+  <si>
+    <t>Neurosen/Persönlichkeitsstörungen/Eßstörungen</t>
+  </si>
+  <si>
+    <t>HDG20.13</t>
+  </si>
+  <si>
+    <t>Alkoholismus</t>
+  </si>
+  <si>
+    <t>HDG20.14</t>
+  </si>
+  <si>
+    <t>Medikamenten-, Drogenabhängigkeit</t>
+  </si>
+  <si>
+    <t>HDG20.15</t>
+  </si>
+  <si>
+    <t>Funktionelle Störungen psychischen Ursprungs</t>
+  </si>
+  <si>
+    <t>HDG20.16</t>
+  </si>
+  <si>
+    <t>Spezielle emotionale Störungen des Kindes- und Jugendalters</t>
+  </si>
+  <si>
+    <t>HDG20.17</t>
+  </si>
+  <si>
+    <t>Oligophrenien</t>
+  </si>
+  <si>
+    <t>HDG21.01</t>
+  </si>
+  <si>
+    <t>Vergiftungen</t>
+  </si>
+  <si>
+    <t>HDG21.03</t>
+  </si>
+  <si>
+    <t>Toxische Wirkungen exogener Noxen</t>
+  </si>
+  <si>
+    <t>HDG22.01</t>
+  </si>
+  <si>
+    <t>Schwerwiegende akute Zustände und Komplikationen</t>
+  </si>
+  <si>
+    <t>HDG22.03</t>
+  </si>
+  <si>
+    <t>Tod und Todesursachen</t>
+  </si>
+  <si>
+    <t>HDG22.04</t>
+  </si>
+  <si>
+    <t>Komplikationen nach Verletzungen und chirurgischen Eingriffen</t>
+  </si>
+  <si>
+    <t>HDG22.05</t>
+  </si>
+  <si>
+    <t>Schädigungen durch äußere Einflüsse</t>
+  </si>
+  <si>
+    <t>HDG23.02</t>
+  </si>
+  <si>
+    <t>Verdacht auf Neoplasie</t>
+  </si>
+  <si>
+    <t>HDG23.03</t>
+  </si>
+  <si>
+    <t>Andere Faktoren zur Inanspruchnahme des Gesundheitswesens</t>
+  </si>
+  <si>
     <t>HDG24.01</t>
   </si>
   <si>
+    <t>Chromosomenanomalien</t>
+  </si>
+  <si>
     <t>HDG24.02</t>
   </si>
   <si>
+    <t>Andere kongenitale Anomalien</t>
+  </si>
+  <si>
     <t>HDG24.03</t>
+  </si>
+  <si>
+    <t>Sonstige unspezifische Befunde</t>
   </si>
   <si>
     <t>System URI</t>
@@ -370,7 +1681,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B223"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -390,39 +1701,1775 @@
         <v>27</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>20</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>31</v>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="B125" t="s" s="2">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="B126" t="s" s="2">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="B127" t="s" s="2">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="B135" t="s" s="2">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="B136" t="s" s="2">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="B137" t="s" s="2">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="B138" t="s" s="2">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="B139" t="s" s="2">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="B140" t="s" s="2">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="B141" t="s" s="2">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="B142" t="s" s="2">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="B143" t="s" s="2">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="B144" t="s" s="2">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="B145" t="s" s="2">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="B146" t="s" s="2">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="B147" t="s" s="2">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="B148" t="s" s="2">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="B149" t="s" s="2">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="B150" t="s" s="2">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="B151" t="s" s="2">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="B152" t="s" s="2">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="B153" t="s" s="2">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="B154" t="s" s="2">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="B155" t="s" s="2">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="B156" t="s" s="2">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="B157" t="s" s="2">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="B158" t="s" s="2">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="B159" t="s" s="2">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="B160" t="s" s="2">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="B161" t="s" s="2">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="B162" t="s" s="2">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="B163" t="s" s="2">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="B164" t="s" s="2">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="B165" t="s" s="2">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="B166" t="s" s="2">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="B167" t="s" s="2">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="B168" t="s" s="2">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="B169" t="s" s="2">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="B170" t="s" s="2">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="B171" t="s" s="2">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="B172" t="s" s="2">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="B173" t="s" s="2">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="B174" t="s" s="2">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="B175" t="s" s="2">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="B176" t="s" s="2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="B177" t="s" s="2">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="B178" t="s" s="2">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="B179" t="s" s="2">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="B180" t="s" s="2">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="B181" t="s" s="2">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="B182" t="s" s="2">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="B183" t="s" s="2">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="B184" t="s" s="2">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="B185" t="s" s="2">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="B186" t="s" s="2">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="B187" t="s" s="2">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="B188" t="s" s="2">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="B189" t="s" s="2">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="B190" t="s" s="2">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="B191" t="s" s="2">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="B192" t="s" s="2">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="B193" t="s" s="2">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="B194" t="s" s="2">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="B195" t="s" s="2">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="B196" t="s" s="2">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="B197" t="s" s="2">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="B198" t="s" s="2">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="B199" t="s" s="2">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="B200" t="s" s="2">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="B201" t="s" s="2">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="B202" t="s" s="2">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="B203" t="s" s="2">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="B204" t="s" s="2">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="B205" t="s" s="2">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="B206" t="s" s="2">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="B207" t="s" s="2">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="B208" t="s" s="2">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="B209" t="s" s="2">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="B210" t="s" s="2">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="B211" t="s" s="2">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="B212" t="s" s="2">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="B213" t="s" s="2">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="B214" t="s" s="2">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="B215" t="s" s="2">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="B216" t="s" s="2">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="B217" t="s" s="2">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="B218" t="s" s="2">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="B219" t="s" s="2">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="B220" t="s" s="2">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="B221" t="s" s="2">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B222" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="B223" t="s" s="2">
+        <v>468</v>
       </c>
     </row>
   </sheetData>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFHauptdiagnosegruppen-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFHauptdiagnosegruppen-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:29:22+00:00</t>
+    <t>2025-02-13T14:40:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFHauptdiagnosegruppen-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFHauptdiagnosegruppen-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:40:19+00:00</t>
+    <t>2025-02-13T14:46:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFHauptdiagnosegruppen-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFHauptdiagnosegruppen-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:46:33+00:00</t>
+    <t>2025-02-13T14:59:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFHauptdiagnosegruppen-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFHauptdiagnosegruppen-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:59:23+00:00</t>
+    <t>2025-02-14T09:24:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFHauptdiagnosegruppen-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFHauptdiagnosegruppen-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:24:21+00:00</t>
+    <t>2025-02-14T09:29:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFHauptdiagnosegruppen-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFHauptdiagnosegruppen-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:29:02+00:00</t>
+    <t>2025-02-14T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFHauptdiagnosegruppen-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFHauptdiagnosegruppen-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:34:15+00:00</t>
+    <t>2025-02-19T07:14:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFHauptdiagnosegruppen-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFHauptdiagnosegruppen-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T07:14:32+00:00</t>
+    <t>2025-02-19T08:04:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFHauptdiagnosegruppen-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFHauptdiagnosegruppen-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T08:04:21+00:00</t>
+    <t>2025-02-19T15:11:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFHauptdiagnosegruppen-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFHauptdiagnosegruppen-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T15:11:41+00:00</t>
+    <t>2025-02-19T15:18:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFHauptdiagnosegruppen-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFHauptdiagnosegruppen-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T15:18:38+00:00</t>
+    <t>2025-02-19T15:36:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
